--- a/Result/profitability/4561.xlsx
+++ b/Result/profitability/4561.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM45"/>
+  <dimension ref="A1:AM46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6145,6 +6145,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4561</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>333</v>
+      </c>
+      <c r="D46" t="n">
+        <v>241</v>
+      </c>
+      <c r="E46" t="n">
+        <v>91</v>
+      </c>
+      <c r="F46" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="G46" t="n">
+        <v>58</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>17.36%</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>61</v>
+      </c>
+      <c r="K46" t="n">
+        <v>49</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="N46" t="n">
+        <v>23.83625</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.1914893617021276</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-4.652173913043478</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.4269370774830994</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
